--- a/Resumo Mágico.xlsx
+++ b/Resumo Mágico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72295D7B-74D6-490F-9711-9D96B92178C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30ADB73F-EE8C-4CA4-9827-E3FE482BAD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2B6AF7-4A38-4DAB-A908-C453FB616B02}"/>
   </bookViews>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11435" uniqueCount="2946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11465" uniqueCount="2949">
   <si>
     <t>Nome da Origem</t>
   </si>
@@ -8927,6 +8927,15 @@
   </si>
   <si>
     <t>Elves of Deepshadow</t>
+  </si>
+  <si>
+    <t>Mind's Dilation</t>
+  </si>
+  <si>
+    <t>Trocar cor do Shield</t>
+  </si>
+  <si>
+    <t>Surrak, Elusive Hunter</t>
   </si>
 </sst>
 </file>
@@ -9226,6 +9235,9 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -9246,9 +9258,6 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -9434,12 +9443,12 @@
     <sortCondition ref="B1:B591"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D7A5AA3F-FE39-4235-A765-A9C286A9FEDA}" uniqueName="1" name="Nome da Origem" queryTableFieldId="1" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{267283B3-42F9-4E10-AF20-93946C15883F}" uniqueName="2" name="Carta Ideal" queryTableFieldId="2" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{2BC98D3A-C3DE-4D74-8C15-9FAE0D8E45CE}" uniqueName="4" name="Em Uso" queryTableFieldId="3" dataDxfId="23">
+    <tableColumn id="1" xr3:uid="{D7A5AA3F-FE39-4235-A765-A9C286A9FEDA}" uniqueName="1" name="Nome da Origem" queryTableFieldId="1" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{267283B3-42F9-4E10-AF20-93946C15883F}" uniqueName="2" name="Carta Ideal" queryTableFieldId="2" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{2BC98D3A-C3DE-4D74-8C15-9FAE0D8E45CE}" uniqueName="4" name="Em Uso" queryTableFieldId="3" dataDxfId="24">
       <calculatedColumnFormula>IF(COUNTIF(Substitutas!$B:$B, B2) &gt; 0, "✅ Tenho", "❌ Faltando")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{EE79FDB7-2F40-4E98-B1B1-9C7B13199B3A}" uniqueName="6" name="Deck" queryTableFieldId="4" dataDxfId="22">
+    <tableColumn id="6" xr3:uid="{EE79FDB7-2F40-4E98-B1B1-9C7B13199B3A}" uniqueName="6" name="Deck" queryTableFieldId="4" dataDxfId="23">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2, Substitutas!$B:$B, Substitutas!$A:$A, "-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9454,10 +9463,10 @@
     <sortCondition ref="C1:C471"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{136DAB5E-F6E8-4E38-B393-57A1CC557F26}" uniqueName="1" name="Nome da Origem" queryTableFieldId="1" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{20BDDFF5-052D-4572-BD7C-6952A4DDE335}" uniqueName="2" name="Carta Ideal" queryTableFieldId="2" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{BDE1CC5D-F74F-4DA8-BFE2-68FD3F94C0CC}" uniqueName="3" name="API.prices.usd" queryTableFieldId="3" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{D0827A6F-FCCE-44AD-A99B-372FA9ADA439}" uniqueName="4" name="Faixa" queryTableFieldId="4" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{136DAB5E-F6E8-4E38-B393-57A1CC557F26}" uniqueName="1" name="Nome da Origem" queryTableFieldId="1" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{20BDDFF5-052D-4572-BD7C-6952A4DDE335}" uniqueName="2" name="Carta Ideal" queryTableFieldId="2" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{BDE1CC5D-F74F-4DA8-BFE2-68FD3F94C0CC}" uniqueName="3" name="API.prices.usd" queryTableFieldId="3" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{D0827A6F-FCCE-44AD-A99B-372FA9ADA439}" uniqueName="4" name="Faixa" queryTableFieldId="4" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9467,7 +9476,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{76E493AC-9A83-48A9-9250-90D1DDACEAAC}" name="Substitutas" displayName="Substitutas" ref="A1:B432" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:B432" xr:uid="{76E493AC-9A83-48A9-9250-90D1DDACEAAC}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{94B465EB-17B2-4E1D-8935-9AA013E87B9B}" uniqueName="1" name="Nome da Origem" queryTableFieldId="1" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{94B465EB-17B2-4E1D-8935-9AA013E87B9B}" uniqueName="1" name="Nome da Origem" queryTableFieldId="1" dataDxfId="18"/>
     <tableColumn id="2" xr3:uid="{9229598C-F1C3-4EE7-998A-825FDB2E7B99}" uniqueName="2" name="Carta Atual" queryTableFieldId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -9481,7 +9490,7 @@
     <sortCondition ref="B1:B2736"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B5D7FC57-0D35-4EC6-A8E9-4D721D5F6F30}" uniqueName="1" name="Nome da Origem" queryTableFieldId="1" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{B5D7FC57-0D35-4EC6-A8E9-4D721D5F6F30}" uniqueName="1" name="Nome da Origem" queryTableFieldId="1" dataDxfId="17"/>
     <tableColumn id="2" xr3:uid="{3F580A46-4796-4AC1-A585-292C85A60BC4}" uniqueName="2" name="Carta Atual" queryTableFieldId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -10216,8 +10225,14 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
+      <c r="L22" t="s">
+        <v>323</v>
+      </c>
       <c r="M22" t="s">
         <v>2939</v>
+      </c>
+      <c r="N22" t="s">
+        <v>1140</v>
       </c>
       <c r="O22" t="s">
         <v>2943</v>
@@ -10342,48 +10357,136 @@
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B31" s="11"/>
       <c r="K31" s="12"/>
+      <c r="L31" t="s">
+        <v>332</v>
+      </c>
+      <c r="M31" t="s">
+        <v>2946</v>
+      </c>
+      <c r="N31" t="s">
+        <v>1966</v>
+      </c>
+      <c r="O31" t="s">
+        <v>2947</v>
+      </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K32" s="12"/>
-    </row>
-    <row r="33" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="L32" t="s">
+        <v>326</v>
+      </c>
+      <c r="M32" t="s">
+        <v>63</v>
+      </c>
+      <c r="N32" t="s">
+        <v>737</v>
+      </c>
+      <c r="O32" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="33" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K33" s="12"/>
-    </row>
-    <row r="34" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="L33" t="s">
+        <v>337</v>
+      </c>
+      <c r="M33" t="s">
+        <v>147</v>
+      </c>
+      <c r="N33" t="s">
+        <v>794</v>
+      </c>
+      <c r="O33" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="34" spans="8:15" x14ac:dyDescent="0.25">
       <c r="H34" s="13"/>
       <c r="K34" s="12"/>
-    </row>
-    <row r="37" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="L34" t="s">
+        <v>333</v>
+      </c>
+      <c r="M34" t="s">
+        <v>2948</v>
+      </c>
+      <c r="N34" t="s">
+        <v>2062</v>
+      </c>
+      <c r="O34" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="35" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="L35" t="s">
+        <v>351</v>
+      </c>
+      <c r="M35" t="s">
+        <v>2147</v>
+      </c>
+      <c r="N35" t="s">
+        <v>1456</v>
+      </c>
+      <c r="O35" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="36" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="L36" t="s">
+        <v>346</v>
+      </c>
+      <c r="M36" t="s">
+        <v>2257</v>
+      </c>
+      <c r="N36" t="s">
+        <v>692</v>
+      </c>
+      <c r="O36" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="37" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K37" s="12"/>
-    </row>
-    <row r="38" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="L37" t="s">
+        <v>1315</v>
+      </c>
+      <c r="M37" t="s">
+        <v>2062</v>
+      </c>
+      <c r="N37" t="s">
+        <v>963</v>
+      </c>
+      <c r="O37" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="38" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K38" s="12"/>
     </row>
-    <row r="39" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K39" s="12"/>
     </row>
-    <row r="40" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K40" s="12"/>
     </row>
-    <row r="41" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K41" s="12"/>
     </row>
-    <row r="42" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K42" s="12"/>
     </row>
-    <row r="44" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K44" s="12"/>
     </row>
-    <row r="45" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K45" s="12"/>
     </row>
-    <row r="46" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K46" s="12"/>
     </row>
-    <row r="47" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K47" s="12"/>
     </row>
-    <row r="48" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K48" s="12"/>
     </row>
     <row r="51" spans="10:11" x14ac:dyDescent="0.25">

--- a/Resumo Mágico.xlsx
+++ b/Resumo Mágico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30ADB73F-EE8C-4CA4-9827-E3FE482BAD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC60C12-B0E8-4154-A9A7-DCD0F1180510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2B6AF7-4A38-4DAB-A908-C453FB616B02}"/>
   </bookViews>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11465" uniqueCount="2949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11481" uniqueCount="2952">
   <si>
     <t>Nome da Origem</t>
   </si>
@@ -8936,6 +8936,15 @@
   </si>
   <si>
     <t>Surrak, Elusive Hunter</t>
+  </si>
+  <si>
+    <t>Ark of Hunger</t>
+  </si>
+  <si>
+    <t>Scheming Silvertong // Sign in Blood</t>
+  </si>
+  <si>
+    <t>Return the Favor</t>
   </si>
 </sst>
 </file>
@@ -10220,7 +10229,7 @@
         <v>883</v>
       </c>
       <c r="O21" t="s">
-        <v>1103</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -10461,15 +10470,63 @@
     </row>
     <row r="38" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K38" s="12"/>
+      <c r="L38" t="s">
+        <v>1068</v>
+      </c>
+      <c r="M38" t="s">
+        <v>2949</v>
+      </c>
+      <c r="N38" t="s">
+        <v>969</v>
+      </c>
+      <c r="O38" t="s">
+        <v>2943</v>
+      </c>
     </row>
     <row r="39" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K39" s="12"/>
+      <c r="L39" t="s">
+        <v>1218</v>
+      </c>
+      <c r="M39" t="s">
+        <v>1684</v>
+      </c>
+      <c r="N39" t="s">
+        <v>1854</v>
+      </c>
+      <c r="O39" t="s">
+        <v>2943</v>
+      </c>
     </row>
     <row r="40" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K40" s="12"/>
+      <c r="L40" t="s">
+        <v>1315</v>
+      </c>
+      <c r="M40" t="s">
+        <v>2950</v>
+      </c>
+      <c r="N40" t="s">
+        <v>1289</v>
+      </c>
+      <c r="O40" t="s">
+        <v>2943</v>
+      </c>
     </row>
     <row r="41" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K41" s="12"/>
+      <c r="L41" t="s">
+        <v>342</v>
+      </c>
+      <c r="M41" t="s">
+        <v>2951</v>
+      </c>
+      <c r="N41" t="s">
+        <v>741</v>
+      </c>
+      <c r="O41" t="s">
+        <v>2943</v>
+      </c>
     </row>
     <row r="42" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K42" s="12"/>

--- a/Resumo Mágico.xlsx
+++ b/Resumo Mágico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC60C12-B0E8-4154-A9A7-DCD0F1180510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119E9573-DD86-43F7-90B9-6D4DE4F1ED92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2B6AF7-4A38-4DAB-A908-C453FB616B02}"/>
   </bookViews>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11481" uniqueCount="2952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11516" uniqueCount="2952">
   <si>
     <t>Nome da Origem</t>
   </si>
@@ -9839,7 +9839,7 @@
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" customWidth="1"/>
+    <col min="15" max="15" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9899,16 +9899,16 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>684</v>
+        <v>2944</v>
       </c>
       <c r="M2" t="s">
-        <v>23</v>
+        <v>927</v>
       </c>
       <c r="N2" t="s">
-        <v>907</v>
+        <v>2945</v>
       </c>
       <c r="O2" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -9925,16 +9925,16 @@
       </c>
       <c r="K3" s="12"/>
       <c r="L3" t="s">
-        <v>684</v>
+        <v>327</v>
       </c>
       <c r="M3" t="s">
-        <v>3</v>
+        <v>1174</v>
       </c>
       <c r="N3" t="s">
-        <v>980</v>
+        <v>1171</v>
       </c>
       <c r="O3" t="s">
-        <v>2943</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -9948,16 +9948,16 @@
       </c>
       <c r="K4" s="12"/>
       <c r="L4" t="s">
-        <v>324</v>
+        <v>684</v>
       </c>
       <c r="M4" t="s">
-        <v>2938</v>
+        <v>23</v>
       </c>
       <c r="N4" t="s">
-        <v>927</v>
+        <v>907</v>
       </c>
       <c r="O4" t="s">
-        <v>2943</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -9972,16 +9972,16 @@
       <c r="J5" s="13"/>
       <c r="K5" s="12"/>
       <c r="L5" t="s">
-        <v>324</v>
+        <v>1315</v>
       </c>
       <c r="M5" t="s">
-        <v>2356</v>
+        <v>2062</v>
       </c>
       <c r="N5" t="s">
-        <v>731</v>
+        <v>963</v>
       </c>
       <c r="O5" t="s">
-        <v>2943</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -9994,32 +9994,29 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>326</v>
+        <v>1116</v>
       </c>
       <c r="M6" t="s">
-        <v>1176</v>
-      </c>
-      <c r="N6" t="s">
-        <v>736</v>
+        <v>1131</v>
       </c>
       <c r="O6" t="s">
-        <v>2943</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="11"/>
       <c r="L7" t="s">
-        <v>327</v>
+        <v>1218</v>
       </c>
       <c r="M7" t="s">
-        <v>1174</v>
+        <v>1327</v>
       </c>
       <c r="N7" t="s">
-        <v>1171</v>
+        <v>691</v>
       </c>
       <c r="O7" t="s">
-        <v>324</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -10027,10 +10024,10 @@
       <c r="G8" s="13"/>
       <c r="K8" s="12"/>
       <c r="L8" t="s">
-        <v>1116</v>
+        <v>1315</v>
       </c>
       <c r="M8" t="s">
-        <v>1131</v>
+        <v>1241</v>
       </c>
       <c r="O8" t="s">
         <v>1172</v>
@@ -10041,16 +10038,16 @@
       <c r="B9" s="11"/>
       <c r="K9" s="12"/>
       <c r="L9" t="s">
-        <v>1023</v>
+        <v>346</v>
       </c>
       <c r="M9" t="s">
-        <v>1951</v>
+        <v>2257</v>
       </c>
       <c r="N9" t="s">
-        <v>1989</v>
+        <v>692</v>
       </c>
       <c r="O9" t="s">
-        <v>2943</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -10058,13 +10055,10 @@
       <c r="B10" s="11"/>
       <c r="J10" s="13"/>
       <c r="L10" t="s">
-        <v>1218</v>
+        <v>1315</v>
       </c>
       <c r="M10" t="s">
-        <v>1326</v>
-      </c>
-      <c r="N10" t="s">
-        <v>691</v>
+        <v>1249</v>
       </c>
       <c r="O10" t="s">
         <v>1172</v>
@@ -10074,13 +10068,10 @@
       <c r="A11" s="1"/>
       <c r="B11" s="11"/>
       <c r="L11" t="s">
-        <v>1218</v>
+        <v>1315</v>
       </c>
       <c r="M11" t="s">
-        <v>1327</v>
-      </c>
-      <c r="N11" t="s">
-        <v>691</v>
+        <v>1248</v>
       </c>
       <c r="O11" t="s">
         <v>1172</v>
@@ -10090,29 +10081,32 @@
       <c r="A12" s="1"/>
       <c r="K12" s="12"/>
       <c r="L12" t="s">
-        <v>2944</v>
+        <v>1218</v>
       </c>
       <c r="M12" t="s">
-        <v>927</v>
+        <v>1326</v>
       </c>
       <c r="N12" t="s">
-        <v>2945</v>
+        <v>691</v>
       </c>
       <c r="O12" t="s">
-        <v>324</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="K13" s="12"/>
       <c r="L13" t="s">
-        <v>1069</v>
+        <v>351</v>
       </c>
       <c r="M13" t="s">
-        <v>1107</v>
+        <v>2147</v>
+      </c>
+      <c r="N13" t="s">
+        <v>1456</v>
       </c>
       <c r="O13" t="s">
-        <v>2943</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -10120,13 +10114,16 @@
       <c r="B14" s="11"/>
       <c r="K14" s="12"/>
       <c r="L14" t="s">
-        <v>1069</v>
+        <v>333</v>
       </c>
       <c r="M14" t="s">
-        <v>1261</v>
+        <v>2948</v>
+      </c>
+      <c r="N14" t="s">
+        <v>2062</v>
       </c>
       <c r="O14" t="s">
-        <v>2943</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -10137,7 +10134,7 @@
         <v>1315</v>
       </c>
       <c r="M15" t="s">
-        <v>1249</v>
+        <v>1234</v>
       </c>
       <c r="O15" t="s">
         <v>1172</v>
@@ -10148,10 +10145,13 @@
       <c r="B16" s="11"/>
       <c r="K16" s="12"/>
       <c r="L16" t="s">
-        <v>1315</v>
+        <v>337</v>
       </c>
       <c r="M16" t="s">
-        <v>1241</v>
+        <v>147</v>
+      </c>
+      <c r="N16" t="s">
+        <v>794</v>
       </c>
       <c r="O16" t="s">
         <v>1172</v>
@@ -10161,10 +10161,13 @@
       <c r="A17" s="1"/>
       <c r="K17" s="12"/>
       <c r="L17" t="s">
-        <v>1315</v>
+        <v>326</v>
       </c>
       <c r="M17" t="s">
-        <v>1234</v>
+        <v>63</v>
+      </c>
+      <c r="N17" t="s">
+        <v>737</v>
       </c>
       <c r="O17" t="s">
         <v>1172</v>
@@ -10174,26 +10177,29 @@
       <c r="A18" s="1"/>
       <c r="H18" s="13"/>
       <c r="L18" t="s">
-        <v>1315</v>
+        <v>1068</v>
       </c>
       <c r="M18" t="s">
-        <v>1248</v>
+        <v>2949</v>
+      </c>
+      <c r="N18" t="s">
+        <v>969</v>
       </c>
       <c r="O18" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="11"/>
       <c r="L19" t="s">
-        <v>1315</v>
+        <v>1218</v>
       </c>
       <c r="M19" t="s">
-        <v>1255</v>
+        <v>1684</v>
       </c>
       <c r="N19" t="s">
-        <v>1309</v>
+        <v>1854</v>
       </c>
       <c r="O19" t="s">
         <v>2943</v>
@@ -10204,13 +10210,13 @@
       <c r="B20" s="11"/>
       <c r="K20" s="12"/>
       <c r="L20" t="s">
-        <v>1315</v>
+        <v>342</v>
       </c>
       <c r="M20" t="s">
-        <v>1250</v>
+        <v>2951</v>
       </c>
       <c r="N20" t="s">
-        <v>1307</v>
+        <v>741</v>
       </c>
       <c r="O20" t="s">
         <v>2943</v>
@@ -10220,56 +10226,62 @@
       <c r="A21" s="1"/>
       <c r="B21" s="11"/>
       <c r="L21" t="s">
-        <v>353</v>
+        <v>1315</v>
       </c>
       <c r="M21" t="s">
-        <v>969</v>
+        <v>2950</v>
       </c>
       <c r="N21" t="s">
-        <v>883</v>
+        <v>1289</v>
       </c>
       <c r="O21" t="s">
-        <v>1068</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="L22" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="M22" t="s">
-        <v>2939</v>
+        <v>2522</v>
       </c>
       <c r="N22" t="s">
-        <v>1140</v>
+        <v>892</v>
       </c>
       <c r="O22" t="s">
-        <v>2943</v>
+        <v>344</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="L23" t="s">
-        <v>1103</v>
+        <v>1068</v>
       </c>
       <c r="M23" t="s">
-        <v>1481</v>
+        <v>892</v>
+      </c>
+      <c r="N23" t="s">
+        <v>850</v>
       </c>
       <c r="O23" t="s">
-        <v>2943</v>
+        <v>347</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="11"/>
       <c r="L24" t="s">
-        <v>1103</v>
+        <v>353</v>
       </c>
       <c r="M24" t="s">
-        <v>2874</v>
+        <v>969</v>
+      </c>
+      <c r="N24" t="s">
+        <v>883</v>
       </c>
       <c r="O24" t="s">
-        <v>2943</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -10277,29 +10289,29 @@
       <c r="B25" s="11"/>
       <c r="K25" s="12"/>
       <c r="L25" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="M25" t="s">
-        <v>2940</v>
+        <v>2946</v>
       </c>
       <c r="N25" t="s">
-        <v>911</v>
+        <v>1966</v>
       </c>
       <c r="O25" t="s">
-        <v>2943</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="11"/>
       <c r="L26" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="M26" t="s">
-        <v>2941</v>
+        <v>2938</v>
       </c>
       <c r="N26" t="s">
-        <v>2522</v>
+        <v>927</v>
       </c>
       <c r="O26" t="s">
         <v>2943</v>
@@ -10311,10 +10323,10 @@
         <v>326</v>
       </c>
       <c r="M27" t="s">
-        <v>2942</v>
+        <v>1176</v>
       </c>
       <c r="N27" t="s">
-        <v>691</v>
+        <v>736</v>
       </c>
       <c r="O27" t="s">
         <v>2943</v>
@@ -10323,10 +10335,13 @@
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="L28" t="s">
-        <v>1103</v>
+        <v>324</v>
       </c>
       <c r="M28" t="s">
-        <v>1592</v>
+        <v>2356</v>
+      </c>
+      <c r="N28" t="s">
+        <v>731</v>
       </c>
       <c r="O28" t="s">
         <v>2943</v>
@@ -10336,148 +10351,136 @@
       <c r="A29" s="1"/>
       <c r="B29" s="11"/>
       <c r="L29" t="s">
-        <v>347</v>
+        <v>1069</v>
       </c>
       <c r="M29" t="s">
-        <v>2522</v>
-      </c>
-      <c r="N29" t="s">
-        <v>892</v>
+        <v>1107</v>
       </c>
       <c r="O29" t="s">
-        <v>344</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B30" s="11"/>
       <c r="L30" t="s">
-        <v>1068</v>
+        <v>1315</v>
       </c>
       <c r="M30" t="s">
-        <v>892</v>
+        <v>1255</v>
       </c>
       <c r="N30" t="s">
-        <v>850</v>
+        <v>1309</v>
       </c>
       <c r="O30" t="s">
-        <v>347</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B31" s="11"/>
       <c r="K31" s="12"/>
       <c r="L31" t="s">
-        <v>332</v>
+        <v>1315</v>
       </c>
       <c r="M31" t="s">
-        <v>2946</v>
+        <v>1250</v>
       </c>
       <c r="N31" t="s">
-        <v>1966</v>
+        <v>1307</v>
       </c>
       <c r="O31" t="s">
-        <v>2947</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K32" s="12"/>
       <c r="L32" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="M32" t="s">
-        <v>63</v>
+        <v>2939</v>
       </c>
       <c r="N32" t="s">
-        <v>737</v>
+        <v>1140</v>
       </c>
       <c r="O32" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="33" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K33" s="12"/>
       <c r="L33" t="s">
-        <v>337</v>
+        <v>1103</v>
       </c>
       <c r="M33" t="s">
-        <v>147</v>
-      </c>
-      <c r="N33" t="s">
-        <v>794</v>
+        <v>1481</v>
       </c>
       <c r="O33" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="34" spans="8:15" x14ac:dyDescent="0.25">
       <c r="H34" s="13"/>
       <c r="K34" s="12"/>
       <c r="L34" t="s">
-        <v>333</v>
+        <v>1023</v>
       </c>
       <c r="M34" t="s">
-        <v>2948</v>
+        <v>1951</v>
       </c>
       <c r="N34" t="s">
-        <v>2062</v>
+        <v>1989</v>
       </c>
       <c r="O34" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="35" spans="8:15" x14ac:dyDescent="0.25">
       <c r="L35" t="s">
-        <v>351</v>
+        <v>1103</v>
       </c>
       <c r="M35" t="s">
-        <v>2147</v>
-      </c>
-      <c r="N35" t="s">
-        <v>1456</v>
+        <v>2874</v>
       </c>
       <c r="O35" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="36" spans="8:15" x14ac:dyDescent="0.25">
       <c r="L36" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M36" t="s">
-        <v>2257</v>
+        <v>2940</v>
       </c>
       <c r="N36" t="s">
-        <v>692</v>
+        <v>911</v>
       </c>
       <c r="O36" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="37" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K37" s="12"/>
       <c r="L37" t="s">
-        <v>1315</v>
+        <v>1069</v>
       </c>
       <c r="M37" t="s">
-        <v>2062</v>
-      </c>
-      <c r="N37" t="s">
-        <v>963</v>
+        <v>1261</v>
       </c>
       <c r="O37" t="s">
-        <v>333</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="38" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K38" s="12"/>
       <c r="L38" t="s">
-        <v>1068</v>
+        <v>344</v>
       </c>
       <c r="M38" t="s">
-        <v>2949</v>
+        <v>2941</v>
       </c>
       <c r="N38" t="s">
-        <v>969</v>
+        <v>2522</v>
       </c>
       <c r="O38" t="s">
         <v>2943</v>
@@ -10486,13 +10489,13 @@
     <row r="39" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K39" s="12"/>
       <c r="L39" t="s">
-        <v>1218</v>
+        <v>684</v>
       </c>
       <c r="M39" t="s">
-        <v>1684</v>
+        <v>3</v>
       </c>
       <c r="N39" t="s">
-        <v>1854</v>
+        <v>980</v>
       </c>
       <c r="O39" t="s">
         <v>2943</v>
@@ -10501,13 +10504,13 @@
     <row r="40" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K40" s="12"/>
       <c r="L40" t="s">
-        <v>1315</v>
+        <v>326</v>
       </c>
       <c r="M40" t="s">
-        <v>2950</v>
+        <v>2942</v>
       </c>
       <c r="N40" t="s">
-        <v>1289</v>
+        <v>691</v>
       </c>
       <c r="O40" t="s">
         <v>2943</v>
@@ -10516,13 +10519,10 @@
     <row r="41" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K41" s="12"/>
       <c r="L41" t="s">
-        <v>342</v>
+        <v>1103</v>
       </c>
       <c r="M41" t="s">
-        <v>2951</v>
-      </c>
-      <c r="N41" t="s">
-        <v>741</v>
+        <v>1592</v>
       </c>
       <c r="O41" t="s">
         <v>2943</v>
@@ -10530,64 +10530,175 @@
     </row>
     <row r="42" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K42" s="12"/>
+      <c r="L42" t="s">
+        <v>2944</v>
+      </c>
+      <c r="M42" t="s">
+        <v>1684</v>
+      </c>
+      <c r="N42" t="s">
+        <v>2353</v>
+      </c>
+      <c r="O42" t="s">
+        <v>2943</v>
+      </c>
+    </row>
+    <row r="43" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="L43" t="s">
+        <v>1103</v>
+      </c>
+      <c r="M43" t="s">
+        <v>2950</v>
+      </c>
+      <c r="O43" t="s">
+        <v>2943</v>
+      </c>
     </row>
     <row r="44" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K44" s="12"/>
+      <c r="L44" t="s">
+        <v>1103</v>
+      </c>
+      <c r="M44" t="s">
+        <v>807</v>
+      </c>
+      <c r="O44" t="s">
+        <v>2943</v>
+      </c>
     </row>
     <row r="45" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K45" s="12"/>
+      <c r="L45" t="s">
+        <v>1103</v>
+      </c>
+      <c r="M45" t="s">
+        <v>807</v>
+      </c>
+      <c r="O45" t="s">
+        <v>2943</v>
+      </c>
     </row>
     <row r="46" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K46" s="12"/>
+      <c r="L46" t="s">
+        <v>1103</v>
+      </c>
+      <c r="M46" t="s">
+        <v>807</v>
+      </c>
+      <c r="O46" t="s">
+        <v>2943</v>
+      </c>
     </row>
     <row r="47" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K47" s="12"/>
+      <c r="L47" t="s">
+        <v>346</v>
+      </c>
+      <c r="M47" t="s">
+        <v>1202</v>
+      </c>
+      <c r="N47" t="s">
+        <v>842</v>
+      </c>
+      <c r="O47" t="s">
+        <v>2943</v>
+      </c>
     </row>
     <row r="48" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K48" s="12"/>
-    </row>
-    <row r="51" spans="10:11" x14ac:dyDescent="0.25">
+      <c r="L48" t="s">
+        <v>348</v>
+      </c>
+      <c r="M48" t="s">
+        <v>1176</v>
+      </c>
+      <c r="N48" t="s">
+        <v>1041</v>
+      </c>
+      <c r="O48" t="s">
+        <v>2943</v>
+      </c>
+    </row>
+    <row r="49" spans="10:15" x14ac:dyDescent="0.25">
+      <c r="L49" t="s">
+        <v>1103</v>
+      </c>
+      <c r="M49" t="s">
+        <v>2951</v>
+      </c>
+      <c r="O49" t="s">
+        <v>2943</v>
+      </c>
+    </row>
+    <row r="50" spans="10:15" x14ac:dyDescent="0.25">
+      <c r="L50" t="s">
+        <v>352</v>
+      </c>
+      <c r="M50" t="s">
+        <v>229</v>
+      </c>
+      <c r="N50" t="s">
+        <v>1113</v>
+      </c>
+      <c r="O50" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="51" spans="10:15" x14ac:dyDescent="0.25">
       <c r="J51" s="13"/>
       <c r="K51" s="12"/>
-    </row>
-    <row r="52" spans="10:11" x14ac:dyDescent="0.25">
+      <c r="L51" t="s">
+        <v>1218</v>
+      </c>
+      <c r="M51" t="s">
+        <v>1193</v>
+      </c>
+      <c r="N51" t="s">
+        <v>1283</v>
+      </c>
+      <c r="O51" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="52" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K52" s="12"/>
     </row>
-    <row r="53" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K53" s="12"/>
     </row>
-    <row r="54" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K54" s="12"/>
     </row>
-    <row r="55" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K55" s="12"/>
     </row>
-    <row r="56" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="10:15" x14ac:dyDescent="0.25">
       <c r="J56" s="13"/>
       <c r="K56" s="12"/>
     </row>
-    <row r="57" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K57" s="12"/>
     </row>
-    <row r="58" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K58" s="12"/>
     </row>
-    <row r="59" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K59" s="12"/>
     </row>
-    <row r="60" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K60" s="12"/>
     </row>
-    <row r="61" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K61" s="12"/>
     </row>
-    <row r="62" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K62" s="12"/>
     </row>
-    <row r="63" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K63" s="12"/>
     </row>
-    <row r="64" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K64" s="12"/>
     </row>
     <row r="65" spans="11:11" x14ac:dyDescent="0.25">
@@ -10754,7 +10865,7 @@
   </sheetData>
   <autoFilter ref="L1:P72" xr:uid="{A5D5E808-9FA7-444C-8452-D3A63D543C16}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="L2:P72">
-      <sortCondition ref="L1:L72"/>
+      <sortCondition ref="O1:O72"/>
     </sortState>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M29:M86">

--- a/Resumo Mágico.xlsx
+++ b/Resumo Mágico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119E9573-DD86-43F7-90B9-6D4DE4F1ED92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666FFA0C-5A33-4FD2-99D5-1BDD5D3825AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2B6AF7-4A38-4DAB-A908-C453FB616B02}"/>
   </bookViews>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11516" uniqueCount="2952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11537" uniqueCount="2953">
   <si>
     <t>Nome da Origem</t>
   </si>
@@ -8945,6 +8945,9 @@
   </si>
   <si>
     <t>Return the Favor</t>
+  </si>
+  <si>
+    <t>Grim Affliction</t>
   </si>
 </sst>
 </file>
@@ -10663,25 +10666,88 @@
     </row>
     <row r="52" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K52" s="12"/>
+      <c r="L52" t="s">
+        <v>339</v>
+      </c>
+      <c r="M52" t="s">
+        <v>164</v>
+      </c>
+      <c r="N52" t="s">
+        <v>814</v>
+      </c>
     </row>
     <row r="53" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K53" s="12"/>
+      <c r="L53" t="s">
+        <v>339</v>
+      </c>
+      <c r="M53" t="s">
+        <v>2952</v>
+      </c>
+      <c r="N53" t="s">
+        <v>811</v>
+      </c>
     </row>
     <row r="54" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K54" s="12"/>
+      <c r="L54" t="s">
+        <v>1021</v>
+      </c>
+      <c r="M54" t="s">
+        <v>124</v>
+      </c>
+      <c r="N54" t="s">
+        <v>1057</v>
+      </c>
     </row>
     <row r="55" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K55" s="12"/>
+      <c r="L55" t="s">
+        <v>353</v>
+      </c>
+      <c r="M55" t="s">
+        <v>238</v>
+      </c>
+      <c r="N55" t="s">
+        <v>688</v>
+      </c>
     </row>
     <row r="56" spans="10:15" x14ac:dyDescent="0.25">
       <c r="J56" s="13"/>
       <c r="K56" s="12"/>
+      <c r="L56" t="s">
+        <v>353</v>
+      </c>
+      <c r="M56" t="s">
+        <v>1567</v>
+      </c>
+      <c r="N56" t="s">
+        <v>879</v>
+      </c>
     </row>
     <row r="57" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K57" s="12"/>
+      <c r="L57" t="s">
+        <v>326</v>
+      </c>
+      <c r="M57" t="s">
+        <v>2282</v>
+      </c>
+      <c r="N57" t="s">
+        <v>953</v>
+      </c>
     </row>
     <row r="58" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K58" s="12"/>
+      <c r="L58" t="s">
+        <v>1315</v>
+      </c>
+      <c r="M58" t="s">
+        <v>676</v>
+      </c>
+      <c r="N58" t="s">
+        <v>1292</v>
+      </c>
     </row>
     <row r="59" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K59" s="12"/>

--- a/Resumo Mágico.xlsx
+++ b/Resumo Mágico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666FFA0C-5A33-4FD2-99D5-1BDD5D3825AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7601F44A-AA44-44E9-B723-4A432FD350EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2B6AF7-4A38-4DAB-A908-C453FB616B02}"/>
   </bookViews>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11537" uniqueCount="2953">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11581" uniqueCount="2956">
   <si>
     <t>Nome da Origem</t>
   </si>
@@ -8948,6 +8948,15 @@
   </si>
   <si>
     <t>Grim Affliction</t>
+  </si>
+  <si>
+    <t>Dreamroot Cascade</t>
+  </si>
+  <si>
+    <t>Stormcarved Coast</t>
+  </si>
+  <si>
+    <t>Cubo</t>
   </si>
 </sst>
 </file>
@@ -9902,16 +9911,16 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>2944</v>
+        <v>684</v>
       </c>
       <c r="M2" t="s">
-        <v>927</v>
+        <v>23</v>
       </c>
       <c r="N2" t="s">
-        <v>2945</v>
+        <v>907</v>
       </c>
       <c r="O2" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -9928,16 +9937,16 @@
       </c>
       <c r="K3" s="12"/>
       <c r="L3" t="s">
-        <v>327</v>
+        <v>684</v>
       </c>
       <c r="M3" t="s">
-        <v>1174</v>
+        <v>3</v>
       </c>
       <c r="N3" t="s">
-        <v>1171</v>
+        <v>980</v>
       </c>
       <c r="O3" t="s">
-        <v>324</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -9951,16 +9960,16 @@
       </c>
       <c r="K4" s="12"/>
       <c r="L4" t="s">
-        <v>684</v>
+        <v>323</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>2939</v>
       </c>
       <c r="N4" t="s">
-        <v>907</v>
+        <v>1140</v>
       </c>
       <c r="O4" t="s">
-        <v>331</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -9975,16 +9984,16 @@
       <c r="J5" s="13"/>
       <c r="K5" s="12"/>
       <c r="L5" t="s">
-        <v>1315</v>
+        <v>324</v>
       </c>
       <c r="M5" t="s">
-        <v>2062</v>
+        <v>2938</v>
       </c>
       <c r="N5" t="s">
-        <v>963</v>
+        <v>927</v>
       </c>
       <c r="O5" t="s">
-        <v>333</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -9997,29 +10006,32 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>1116</v>
+        <v>324</v>
       </c>
       <c r="M6" t="s">
-        <v>1131</v>
+        <v>2356</v>
+      </c>
+      <c r="N6" t="s">
+        <v>731</v>
       </c>
       <c r="O6" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="11"/>
       <c r="L7" t="s">
-        <v>1218</v>
+        <v>326</v>
       </c>
       <c r="M7" t="s">
-        <v>1327</v>
+        <v>2282</v>
       </c>
       <c r="N7" t="s">
-        <v>691</v>
+        <v>953</v>
       </c>
       <c r="O7" t="s">
-        <v>1172</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -10027,10 +10039,13 @@
       <c r="G8" s="13"/>
       <c r="K8" s="12"/>
       <c r="L8" t="s">
-        <v>1315</v>
+        <v>326</v>
       </c>
       <c r="M8" t="s">
-        <v>1241</v>
+        <v>63</v>
+      </c>
+      <c r="N8" t="s">
+        <v>737</v>
       </c>
       <c r="O8" t="s">
         <v>1172</v>
@@ -10041,16 +10056,16 @@
       <c r="B9" s="11"/>
       <c r="K9" s="12"/>
       <c r="L9" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="M9" t="s">
-        <v>2257</v>
+        <v>1176</v>
       </c>
       <c r="N9" t="s">
-        <v>692</v>
+        <v>736</v>
       </c>
       <c r="O9" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -10058,58 +10073,55 @@
       <c r="B10" s="11"/>
       <c r="J10" s="13"/>
       <c r="L10" t="s">
-        <v>1315</v>
+        <v>326</v>
       </c>
       <c r="M10" t="s">
-        <v>1249</v>
+        <v>2942</v>
+      </c>
+      <c r="N10" t="s">
+        <v>691</v>
       </c>
       <c r="O10" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="11"/>
       <c r="L11" t="s">
-        <v>1315</v>
+        <v>1103</v>
       </c>
       <c r="M11" t="s">
-        <v>1248</v>
+        <v>1481</v>
       </c>
       <c r="O11" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="K12" s="12"/>
       <c r="L12" t="s">
-        <v>1218</v>
+        <v>1103</v>
       </c>
       <c r="M12" t="s">
-        <v>1326</v>
-      </c>
-      <c r="N12" t="s">
-        <v>691</v>
+        <v>2874</v>
       </c>
       <c r="O12" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="K13" s="12"/>
       <c r="L13" t="s">
-        <v>351</v>
+        <v>1103</v>
       </c>
       <c r="M13" t="s">
-        <v>2147</v>
-      </c>
-      <c r="N13" t="s">
-        <v>1456</v>
+        <v>1592</v>
       </c>
       <c r="O13" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -10117,16 +10129,13 @@
       <c r="B14" s="11"/>
       <c r="K14" s="12"/>
       <c r="L14" t="s">
-        <v>333</v>
+        <v>1103</v>
       </c>
       <c r="M14" t="s">
-        <v>2948</v>
-      </c>
-      <c r="N14" t="s">
-        <v>2062</v>
+        <v>2950</v>
       </c>
       <c r="O14" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -10134,13 +10143,13 @@
       <c r="B15" s="11"/>
       <c r="K15" s="12"/>
       <c r="L15" t="s">
-        <v>1315</v>
+        <v>1103</v>
       </c>
       <c r="M15" t="s">
-        <v>1234</v>
+        <v>807</v>
       </c>
       <c r="O15" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -10148,45 +10157,36 @@
       <c r="B16" s="11"/>
       <c r="K16" s="12"/>
       <c r="L16" t="s">
-        <v>337</v>
+        <v>1103</v>
       </c>
       <c r="M16" t="s">
-        <v>147</v>
-      </c>
-      <c r="N16" t="s">
-        <v>794</v>
+        <v>807</v>
       </c>
       <c r="O16" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="K17" s="12"/>
       <c r="L17" t="s">
-        <v>326</v>
+        <v>1103</v>
       </c>
       <c r="M17" t="s">
-        <v>63</v>
-      </c>
-      <c r="N17" t="s">
-        <v>737</v>
+        <v>807</v>
       </c>
       <c r="O17" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="H18" s="13"/>
       <c r="L18" t="s">
-        <v>1068</v>
+        <v>1103</v>
       </c>
       <c r="M18" t="s">
-        <v>2949</v>
-      </c>
-      <c r="N18" t="s">
-        <v>969</v>
+        <v>2951</v>
       </c>
       <c r="O18" t="s">
         <v>2943</v>
@@ -10196,13 +10196,10 @@
       <c r="A19" s="1"/>
       <c r="B19" s="11"/>
       <c r="L19" t="s">
-        <v>1218</v>
+        <v>2955</v>
       </c>
       <c r="M19" t="s">
-        <v>1684</v>
-      </c>
-      <c r="N19" t="s">
-        <v>1854</v>
+        <v>2368</v>
       </c>
       <c r="O19" t="s">
         <v>2943</v>
@@ -10213,78 +10210,69 @@
       <c r="B20" s="11"/>
       <c r="K20" s="12"/>
       <c r="L20" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="M20" t="s">
-        <v>2951</v>
+        <v>1174</v>
       </c>
       <c r="N20" t="s">
-        <v>741</v>
+        <v>1171</v>
       </c>
       <c r="O20" t="s">
-        <v>2943</v>
+        <v>324</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="11"/>
       <c r="L21" t="s">
-        <v>1315</v>
+        <v>1116</v>
       </c>
       <c r="M21" t="s">
-        <v>2950</v>
-      </c>
-      <c r="N21" t="s">
-        <v>1289</v>
+        <v>1131</v>
       </c>
       <c r="O21" t="s">
-        <v>2943</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="L22" t="s">
-        <v>347</v>
+        <v>1116</v>
       </c>
       <c r="M22" t="s">
-        <v>2522</v>
-      </c>
-      <c r="N22" t="s">
-        <v>892</v>
+        <v>1138</v>
       </c>
       <c r="O22" t="s">
-        <v>344</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="L23" t="s">
-        <v>1068</v>
+        <v>1116</v>
       </c>
       <c r="M23" t="s">
-        <v>892</v>
-      </c>
-      <c r="N23" t="s">
-        <v>850</v>
+        <v>2041</v>
       </c>
       <c r="O23" t="s">
-        <v>347</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="11"/>
       <c r="L24" t="s">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="M24" t="s">
-        <v>969</v>
+        <v>2954</v>
       </c>
       <c r="N24" t="s">
-        <v>883</v>
+        <v>689</v>
       </c>
       <c r="O24" t="s">
-        <v>1068</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -10295,41 +10283,41 @@
         <v>332</v>
       </c>
       <c r="M25" t="s">
-        <v>2946</v>
+        <v>2954</v>
       </c>
       <c r="N25" t="s">
-        <v>1966</v>
+        <v>689</v>
       </c>
       <c r="O25" t="s">
-        <v>2947</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="11"/>
       <c r="L26" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="M26" t="s">
-        <v>2938</v>
+        <v>2946</v>
       </c>
       <c r="N26" t="s">
-        <v>927</v>
+        <v>1966</v>
       </c>
       <c r="O26" t="s">
-        <v>2943</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="L27" t="s">
-        <v>326</v>
+        <v>1023</v>
       </c>
       <c r="M27" t="s">
-        <v>1176</v>
+        <v>1951</v>
       </c>
       <c r="N27" t="s">
-        <v>736</v>
+        <v>1989</v>
       </c>
       <c r="O27" t="s">
         <v>2943</v>
@@ -10338,26 +10326,29 @@
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="L28" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="M28" t="s">
-        <v>2356</v>
+        <v>2948</v>
       </c>
       <c r="N28" t="s">
-        <v>731</v>
+        <v>2062</v>
       </c>
       <c r="O28" t="s">
-        <v>2943</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="11"/>
       <c r="L29" t="s">
-        <v>1069</v>
+        <v>334</v>
       </c>
       <c r="M29" t="s">
-        <v>1107</v>
+        <v>2953</v>
+      </c>
+      <c r="N29" t="s">
+        <v>692</v>
       </c>
       <c r="O29" t="s">
         <v>2943</v>
@@ -10366,83 +10357,89 @@
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B30" s="11"/>
       <c r="L30" t="s">
-        <v>1315</v>
+        <v>1021</v>
       </c>
       <c r="M30" t="s">
-        <v>1255</v>
+        <v>124</v>
       </c>
       <c r="N30" t="s">
-        <v>1309</v>
+        <v>1057</v>
       </c>
       <c r="O30" t="s">
-        <v>2943</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B31" s="11"/>
       <c r="K31" s="12"/>
       <c r="L31" t="s">
-        <v>1315</v>
+        <v>337</v>
       </c>
       <c r="M31" t="s">
-        <v>1250</v>
+        <v>147</v>
       </c>
       <c r="N31" t="s">
-        <v>1307</v>
+        <v>794</v>
       </c>
       <c r="O31" t="s">
-        <v>2943</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K32" s="12"/>
       <c r="L32" t="s">
-        <v>323</v>
+        <v>1218</v>
       </c>
       <c r="M32" t="s">
-        <v>2939</v>
+        <v>1327</v>
       </c>
       <c r="N32" t="s">
-        <v>1140</v>
+        <v>691</v>
       </c>
       <c r="O32" t="s">
-        <v>2943</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="33" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K33" s="12"/>
       <c r="L33" t="s">
-        <v>1103</v>
+        <v>1218</v>
       </c>
       <c r="M33" t="s">
-        <v>1481</v>
+        <v>1326</v>
+      </c>
+      <c r="N33" t="s">
+        <v>691</v>
       </c>
       <c r="O33" t="s">
-        <v>2943</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="34" spans="8:15" x14ac:dyDescent="0.25">
       <c r="H34" s="13"/>
       <c r="K34" s="12"/>
       <c r="L34" t="s">
-        <v>1023</v>
+        <v>1218</v>
       </c>
       <c r="M34" t="s">
-        <v>1951</v>
+        <v>1193</v>
       </c>
       <c r="N34" t="s">
-        <v>1989</v>
+        <v>1283</v>
       </c>
       <c r="O34" t="s">
-        <v>2943</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="35" spans="8:15" x14ac:dyDescent="0.25">
       <c r="L35" t="s">
-        <v>1103</v>
+        <v>1218</v>
       </c>
       <c r="M35" t="s">
-        <v>2874</v>
+        <v>1684</v>
+      </c>
+      <c r="N35" t="s">
+        <v>1854</v>
       </c>
       <c r="O35" t="s">
         <v>2943</v>
@@ -10450,40 +10447,43 @@
     </row>
     <row r="36" spans="8:15" x14ac:dyDescent="0.25">
       <c r="L36" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="M36" t="s">
-        <v>2940</v>
+        <v>164</v>
       </c>
       <c r="N36" t="s">
-        <v>911</v>
+        <v>814</v>
       </c>
       <c r="O36" t="s">
-        <v>2943</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="37" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K37" s="12"/>
       <c r="L37" t="s">
-        <v>1069</v>
+        <v>339</v>
       </c>
       <c r="M37" t="s">
-        <v>1261</v>
+        <v>2952</v>
+      </c>
+      <c r="N37" t="s">
+        <v>811</v>
       </c>
       <c r="O37" t="s">
-        <v>2943</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="38" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K38" s="12"/>
       <c r="L38" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="M38" t="s">
-        <v>2941</v>
+        <v>15</v>
       </c>
       <c r="N38" t="s">
-        <v>2522</v>
+        <v>810</v>
       </c>
       <c r="O38" t="s">
         <v>2943</v>
@@ -10492,13 +10492,13 @@
     <row r="39" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K39" s="12"/>
       <c r="L39" t="s">
-        <v>684</v>
+        <v>339</v>
       </c>
       <c r="M39" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="N39" t="s">
-        <v>980</v>
+        <v>1065</v>
       </c>
       <c r="O39" t="s">
         <v>2943</v>
@@ -10507,25 +10507,28 @@
     <row r="40" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K40" s="12"/>
       <c r="L40" t="s">
-        <v>326</v>
+        <v>2944</v>
       </c>
       <c r="M40" t="s">
-        <v>2942</v>
+        <v>927</v>
       </c>
       <c r="N40" t="s">
-        <v>691</v>
+        <v>2945</v>
       </c>
       <c r="O40" t="s">
-        <v>2943</v>
+        <v>324</v>
       </c>
     </row>
     <row r="41" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K41" s="12"/>
       <c r="L41" t="s">
-        <v>1103</v>
+        <v>2944</v>
       </c>
       <c r="M41" t="s">
-        <v>1592</v>
+        <v>1684</v>
+      </c>
+      <c r="N41" t="s">
+        <v>2353</v>
       </c>
       <c r="O41" t="s">
         <v>2943</v>
@@ -10537,10 +10540,10 @@
         <v>2944</v>
       </c>
       <c r="M42" t="s">
-        <v>1684</v>
+        <v>1200</v>
       </c>
       <c r="N42" t="s">
-        <v>2353</v>
+        <v>965</v>
       </c>
       <c r="O42" t="s">
         <v>2943</v>
@@ -10548,10 +10551,10 @@
     </row>
     <row r="43" spans="8:15" x14ac:dyDescent="0.25">
       <c r="L43" t="s">
-        <v>1103</v>
+        <v>1069</v>
       </c>
       <c r="M43" t="s">
-        <v>2950</v>
+        <v>1107</v>
       </c>
       <c r="O43" t="s">
         <v>2943</v>
@@ -10560,10 +10563,10 @@
     <row r="44" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K44" s="12"/>
       <c r="L44" t="s">
-        <v>1103</v>
+        <v>1069</v>
       </c>
       <c r="M44" t="s">
-        <v>807</v>
+        <v>1261</v>
       </c>
       <c r="O44" t="s">
         <v>2943</v>
@@ -10572,77 +10575,74 @@
     <row r="45" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K45" s="12"/>
       <c r="L45" t="s">
+        <v>1315</v>
+      </c>
+      <c r="M45" t="s">
+        <v>676</v>
+      </c>
+      <c r="N45" t="s">
+        <v>1292</v>
+      </c>
+      <c r="O45" t="s">
         <v>1103</v>
-      </c>
-      <c r="M45" t="s">
-        <v>807</v>
-      </c>
-      <c r="O45" t="s">
-        <v>2943</v>
       </c>
     </row>
     <row r="46" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K46" s="12"/>
       <c r="L46" t="s">
-        <v>1103</v>
+        <v>1315</v>
       </c>
       <c r="M46" t="s">
-        <v>807</v>
+        <v>2062</v>
+      </c>
+      <c r="N46" t="s">
+        <v>963</v>
       </c>
       <c r="O46" t="s">
-        <v>2943</v>
+        <v>333</v>
       </c>
     </row>
     <row r="47" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K47" s="12"/>
       <c r="L47" t="s">
-        <v>346</v>
+        <v>1315</v>
       </c>
       <c r="M47" t="s">
-        <v>1202</v>
-      </c>
-      <c r="N47" t="s">
-        <v>842</v>
+        <v>1241</v>
       </c>
       <c r="O47" t="s">
-        <v>2943</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="48" spans="8:15" x14ac:dyDescent="0.25">
       <c r="K48" s="12"/>
       <c r="L48" t="s">
-        <v>348</v>
+        <v>1315</v>
       </c>
       <c r="M48" t="s">
-        <v>1176</v>
-      </c>
-      <c r="N48" t="s">
-        <v>1041</v>
+        <v>1249</v>
       </c>
       <c r="O48" t="s">
-        <v>2943</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="49" spans="10:15" x14ac:dyDescent="0.25">
       <c r="L49" t="s">
-        <v>1103</v>
+        <v>1315</v>
       </c>
       <c r="M49" t="s">
-        <v>2951</v>
+        <v>1248</v>
       </c>
       <c r="O49" t="s">
-        <v>2943</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="50" spans="10:15" x14ac:dyDescent="0.25">
       <c r="L50" t="s">
-        <v>352</v>
+        <v>1315</v>
       </c>
       <c r="M50" t="s">
-        <v>229</v>
-      </c>
-      <c r="N50" t="s">
-        <v>1113</v>
+        <v>1234</v>
       </c>
       <c r="O50" t="s">
         <v>1172</v>
@@ -10652,146 +10652,287 @@
       <c r="J51" s="13"/>
       <c r="K51" s="12"/>
       <c r="L51" t="s">
-        <v>1218</v>
+        <v>1315</v>
       </c>
       <c r="M51" t="s">
-        <v>1193</v>
+        <v>2950</v>
       </c>
       <c r="N51" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="O51" t="s">
-        <v>1172</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="52" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K52" s="12"/>
       <c r="L52" t="s">
-        <v>339</v>
+        <v>1315</v>
       </c>
       <c r="M52" t="s">
-        <v>164</v>
+        <v>1255</v>
       </c>
       <c r="N52" t="s">
-        <v>814</v>
+        <v>1309</v>
+      </c>
+      <c r="O52" t="s">
+        <v>2943</v>
       </c>
     </row>
     <row r="53" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K53" s="12"/>
       <c r="L53" t="s">
-        <v>339</v>
+        <v>1315</v>
       </c>
       <c r="M53" t="s">
-        <v>2952</v>
+        <v>1250</v>
       </c>
       <c r="N53" t="s">
-        <v>811</v>
+        <v>1307</v>
+      </c>
+      <c r="O53" t="s">
+        <v>2943</v>
       </c>
     </row>
     <row r="54" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K54" s="12"/>
       <c r="L54" t="s">
-        <v>1021</v>
+        <v>342</v>
       </c>
       <c r="M54" t="s">
-        <v>124</v>
+        <v>2951</v>
       </c>
       <c r="N54" t="s">
-        <v>1057</v>
+        <v>741</v>
+      </c>
+      <c r="O54" t="s">
+        <v>2943</v>
       </c>
     </row>
     <row r="55" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K55" s="12"/>
       <c r="L55" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="M55" t="s">
-        <v>238</v>
+        <v>2941</v>
       </c>
       <c r="N55" t="s">
-        <v>688</v>
+        <v>2522</v>
+      </c>
+      <c r="O55" t="s">
+        <v>2943</v>
       </c>
     </row>
     <row r="56" spans="10:15" x14ac:dyDescent="0.25">
       <c r="J56" s="13"/>
       <c r="K56" s="12"/>
       <c r="L56" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="M56" t="s">
-        <v>1567</v>
+        <v>2954</v>
       </c>
       <c r="N56" t="s">
-        <v>879</v>
+        <v>689</v>
+      </c>
+      <c r="O56" t="s">
+        <v>2943</v>
       </c>
     </row>
     <row r="57" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K57" s="12"/>
       <c r="L57" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="M57" t="s">
-        <v>2282</v>
+        <v>2257</v>
       </c>
       <c r="N57" t="s">
-        <v>953</v>
+        <v>692</v>
+      </c>
+      <c r="O57" t="s">
+        <v>1172</v>
       </c>
     </row>
     <row r="58" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K58" s="12"/>
       <c r="L58" t="s">
-        <v>1315</v>
+        <v>346</v>
       </c>
       <c r="M58" t="s">
-        <v>676</v>
+        <v>1202</v>
       </c>
       <c r="N58" t="s">
-        <v>1292</v>
+        <v>842</v>
+      </c>
+      <c r="O58" t="s">
+        <v>2943</v>
       </c>
     </row>
     <row r="59" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K59" s="12"/>
+      <c r="L59" t="s">
+        <v>347</v>
+      </c>
+      <c r="M59" t="s">
+        <v>2522</v>
+      </c>
+      <c r="N59" t="s">
+        <v>892</v>
+      </c>
+      <c r="O59" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="60" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K60" s="12"/>
+      <c r="L60" t="s">
+        <v>1068</v>
+      </c>
+      <c r="M60" t="s">
+        <v>2949</v>
+      </c>
+      <c r="N60" t="s">
+        <v>969</v>
+      </c>
+      <c r="O60" t="s">
+        <v>2943</v>
+      </c>
     </row>
     <row r="61" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K61" s="12"/>
+      <c r="L61" t="s">
+        <v>1068</v>
+      </c>
+      <c r="M61" t="s">
+        <v>892</v>
+      </c>
+      <c r="N61" t="s">
+        <v>850</v>
+      </c>
+      <c r="O61" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="62" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K62" s="12"/>
+      <c r="L62" t="s">
+        <v>348</v>
+      </c>
+      <c r="M62" t="s">
+        <v>1176</v>
+      </c>
+      <c r="N62" t="s">
+        <v>1041</v>
+      </c>
+      <c r="O62" t="s">
+        <v>2943</v>
+      </c>
     </row>
     <row r="63" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K63" s="12"/>
+      <c r="L63" t="s">
+        <v>349</v>
+      </c>
+      <c r="M63" t="s">
+        <v>2940</v>
+      </c>
+      <c r="N63" t="s">
+        <v>911</v>
+      </c>
+      <c r="O63" t="s">
+        <v>2943</v>
+      </c>
     </row>
     <row r="64" spans="10:15" x14ac:dyDescent="0.25">
       <c r="K64" s="12"/>
-    </row>
-    <row r="65" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="L64" t="s">
+        <v>351</v>
+      </c>
+      <c r="M64" t="s">
+        <v>2147</v>
+      </c>
+      <c r="N64" t="s">
+        <v>1456</v>
+      </c>
+      <c r="O64" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="65" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K65" s="12"/>
-    </row>
-    <row r="66" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="L65" t="s">
+        <v>352</v>
+      </c>
+      <c r="M65" t="s">
+        <v>229</v>
+      </c>
+      <c r="N65" t="s">
+        <v>1113</v>
+      </c>
+      <c r="O65" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="66" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K66" s="12"/>
-    </row>
-    <row r="67" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="L66" t="s">
+        <v>353</v>
+      </c>
+      <c r="M66" t="s">
+        <v>238</v>
+      </c>
+      <c r="N66" t="s">
+        <v>688</v>
+      </c>
+      <c r="O66" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="67" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K67" s="12"/>
-    </row>
-    <row r="68" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="L67" t="s">
+        <v>353</v>
+      </c>
+      <c r="M67" t="s">
+        <v>1567</v>
+      </c>
+      <c r="N67" t="s">
+        <v>879</v>
+      </c>
+      <c r="O67" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="68" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K68" s="12"/>
-    </row>
-    <row r="69" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="L68" t="s">
+        <v>353</v>
+      </c>
+      <c r="M68" t="s">
+        <v>969</v>
+      </c>
+      <c r="N68" t="s">
+        <v>883</v>
+      </c>
+      <c r="O68" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="69" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K69" s="12"/>
     </row>
-    <row r="70" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K70" s="12"/>
     </row>
-    <row r="71" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K71" s="12"/>
     </row>
-    <row r="72" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K72" s="12"/>
     </row>
-    <row r="73" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K73" s="12"/>
     </row>
     <row r="91" spans="13:13" x14ac:dyDescent="0.25">
@@ -10931,7 +11072,7 @@
   </sheetData>
   <autoFilter ref="L1:P72" xr:uid="{A5D5E808-9FA7-444C-8452-D3A63D543C16}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="L2:P72">
-      <sortCondition ref="O1:O72"/>
+      <sortCondition ref="L1:L72"/>
     </sortState>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M29:M86">
